--- a/src/data/episodes/1.xlsx
+++ b/src/data/episodes/1.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>الحلقة</t>
   </si>
@@ -25,6 +25,9 @@
     <t>بيانات المقطع</t>
   </si>
   <si>
+    <t>وقوت الصلاة</t>
+  </si>
+  <si>
     <t>كتاب</t>
   </si>
   <si>
@@ -35,6 +38,9 @@
   </si>
   <si>
     <t>اعلام</t>
+  </si>
+  <si>
+    <t>تعريف الباب</t>
   </si>
   <si>
     <t>تعاريف</t>
@@ -56,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -65,6 +71,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -90,10 +100,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -109,16 +127,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -469,11 +487,13 @@
     <col min="1" max="1" width="17.714285714285715" customWidth="1"/>
     <col min="2" max="2" width="41.285714285714285" customWidth="1"/>
     <col min="3" max="3" width="20.142857142857142" customWidth="1"/>
-    <col min="4" max="25" width="13.571428571428571" customWidth="1"/>
+    <col min="4" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1">
+        <v>1</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -494,27 +514,33 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="C4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -523,16 +549,18 @@
       <c r="A6" s="7"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="C7" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -541,20 +569,20 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
